--- a/physician_forms/003_vaccination_plan_survey--physician_forms.xlsx
+++ b/physician_forms/003_vaccination_plan_survey--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>vaccination_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vaccination Plan Survey</t>
+          <t>Vaccination Date</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,40 +538,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vaccination_date</t>
+          <t>vaccination_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>vaccination_date</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Vaccination Time</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Format - HH -MM</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vaccination_time</t>
+          <t>vaccination_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>vaccination_time</t>
+          <t>Vaccination Status</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,23 +588,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vaccination_type</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>vaccination_type</t>
+          <t>Medical Condition</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +616,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vaccination_type</t>
+          <t>vaccination_plan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vaccination_type</t>
+          <t>Vaccination Plan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>vaccination_status</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>vaccination_status</t>
+          <t>Follow Up</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vaccination_status</t>
+          <t>medical_condition_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vaccination_status</t>
+          <t>Medical Condition 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,35 +685,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>is_candidate_for_vaccination</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>Candidate for Vaccination</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>Additional Info</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -781,136 +785,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vaccination_type_choices</t>
+          <t>vaccination_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vaccination_type_choices</t>
+          <t>vaccination_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vaccination_type_choices</t>
+          <t>vaccination_plan_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vaccination_type_choices</t>
+          <t>vaccination_plan_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vaccination_status_choices</t>
+          <t>vaccination_plan_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vaccination_status_choices</t>
+          <t>vaccination_plan_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>vaccination_status_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>vaccination_status_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
